--- a/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
   <si>
     <t>FAF</t>
   </si>
@@ -656,344 +656,351 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2117300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1838000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2049700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1978900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1841300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1582300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1685100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1406100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1612300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1424600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1429300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1481200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1646900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1446100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1715000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1975000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2139000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2105000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2533100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2555900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2266400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2025700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2151300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1913700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1608700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1412900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1728700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1671200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1498600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1303600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1417100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1542200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1491200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1297400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1481300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1519600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1454400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1317000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1504300</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1508300</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>745900</v>
+      </c>
+      <c r="E9" s="3">
         <v>680000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>718700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>730900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>655400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>595600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>637100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>638500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>571700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>517300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>528800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>622500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>585900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>551300</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1069,53 +1076,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1371400</v>
+      </c>
+      <c r="E10" s="3">
         <v>1158000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1331000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1248000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1185900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>986700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1048000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>767600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1040600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>907300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>900500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>858700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1061000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>894800</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1191,8 +1201,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,8 +1496,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1523,39 +1543,39 @@
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-18300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>73300</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1571,8 +1591,8 @@
       <c r="AF14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AH14" s="3">
         <v>0</v>
@@ -1601,130 +1621,136 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>53600</v>
+      </c>
+      <c r="E15" s="3">
         <v>54600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>55900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>54800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>53000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>52500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>52000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>53200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>52100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>50100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>49600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>47300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>46100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>45500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>43000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>41000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>42000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>41000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>39500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>39200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>40900</v>
-      </c>
-      <c r="X15" s="3">
-        <v>38300</v>
       </c>
       <c r="Y15" s="3">
         <v>38300</v>
       </c>
       <c r="Z15" s="3">
+        <v>38300</v>
+      </c>
+      <c r="AA15" s="3">
         <v>38200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>41000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>31400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>31500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>31700</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>32900</v>
       </c>
       <c r="AF15" s="3">
         <v>32900</v>
       </c>
       <c r="AG15" s="3">
+        <v>32900</v>
+      </c>
+      <c r="AH15" s="3">
         <v>33400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>31700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>31100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>29700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>31800</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>36000</v>
-      </c>
-      <c r="AM15" s="3">
-        <v>30100</v>
       </c>
       <c r="AN15" s="3">
         <v>30100</v>
       </c>
       <c r="AO15" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AP15" s="3">
         <v>28100</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1787700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1634300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1718400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1692000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1608100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1450500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1541500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1514300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1425300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1332000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1357600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1447100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1434500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1357400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1597000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1803000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1902000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1884000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2019500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1933500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1850700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1703200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1753000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1654400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1370000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1328500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1428400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1413600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1257200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1150000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1287200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1335800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1279200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1195100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1312800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1492500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1261300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1224400</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1414000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1333600</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>329600</v>
+      </c>
+      <c r="E18" s="3">
         <v>203700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>331300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>286900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>233200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>131800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>143600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-108200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>187000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>92600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>71700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>34100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>212400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>88700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>118000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>172000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>237000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>221000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>513600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>622400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>415700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>322500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>398300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>259300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>238700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>84400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>300300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>257600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>241400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>153600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>129900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>206400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>212000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>102300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>168500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>27100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>193100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>92600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>90300</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>174700</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,8 +2085,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2096,24 +2130,24 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-30000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-151000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-77000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-71000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-160100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -2174,496 +2208,511 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>383200</v>
+      </c>
+      <c r="E21" s="3">
         <v>258300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>387200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>341700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>286200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>184300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>195600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-55000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>239100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>142700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>121300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>81400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>258500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>134200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>131000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>62000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>202000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>191000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>393000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>661600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>456600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>360800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>436600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>297600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>279700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>115900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>331700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>289300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>274300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>186500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>163300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>238100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>243000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>132000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>200300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>63100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>223300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>122700</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>118400</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>199300</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>45700</v>
+      </c>
+      <c r="E22" s="3">
         <v>41900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>43900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>39900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>38000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>35200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>43700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>36200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>35400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>34300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>33300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>35800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>34300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>29100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>30000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>24000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>19000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>20000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>20100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>19200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>16200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>16500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>15900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>16000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>13400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>12100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>11700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>12200</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>11900</v>
       </c>
       <c r="AF22" s="3">
         <v>11900</v>
       </c>
       <c r="AG22" s="3">
+        <v>11900</v>
+      </c>
+      <c r="AH22" s="3">
         <v>11000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>10800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>10000</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>9200</v>
       </c>
       <c r="AK22" s="3">
         <v>9200</v>
       </c>
       <c r="AL22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AM22" s="3">
         <v>9100</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>9000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>8700</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>8800</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>283900</v>
+      </c>
+      <c r="E23" s="3">
         <v>161800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>287400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>247000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>195200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>96600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>99900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-144400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>151600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>58300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>38400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>178100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>59600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>58000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>141000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>130000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>333400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>603200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>399400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>306000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>382300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>243400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>225300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>72300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>288500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>245300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>229500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>141700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>118900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>195600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>202000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>93100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>159300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>18000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>184200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>83900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>81500</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>166900</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>64800</v>
+      </c>
+      <c r="E24" s="3">
         <v>37000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>74000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>57100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>48100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>21800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>27000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-41000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>35200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>11600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>41700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>13600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-6000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>31000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>32000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>72700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>152700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>96000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>71600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>100900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>59800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>53600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>8500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>63900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>57200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>42200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>31900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>25700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>44100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>46900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>16900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>52700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>62300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>25800</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>500</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>219100</v>
+      </c>
+      <c r="E26" s="3">
         <v>124800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>213400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>189900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>147100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>74800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>72900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-103400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>116400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>46700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>34300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>136400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>46000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>54000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>3000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>110000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>98000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>260700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>450500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>303400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>234500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>281400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>183600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>171700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>63800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>224600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>188200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>187300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>109800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>93200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>151500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>155100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>76200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>106600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>21200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>121900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>58100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>81000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>107400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>218500</v>
+      </c>
+      <c r="E27" s="3">
         <v>125100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>211900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>189600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>146100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>74200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>72400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-104000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>116000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>46700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>34100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>138500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>45900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>54000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>109000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>98000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>259800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>445300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>302300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>233600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>280300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>182300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>170700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>63200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>224000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>187200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>186700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>109600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>91600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>151500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>155100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>76200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>107000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>21400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>122300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>58300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>81000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3236,8 +3297,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
@@ -3254,12 +3315,12 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>114100</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,8 +3583,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3560,24 +3630,24 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>30000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>151000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>77000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>71000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>160100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -3638,130 +3708,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>218500</v>
+      </c>
+      <c r="E33" s="3">
         <v>125100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>211900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>189600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>146100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>74200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>72400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-104000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>116000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>46700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>34100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>138500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>45900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>54000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>109000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>98000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>259800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>445300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>302300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>233600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>280300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>182300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>170700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>63200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>224000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>187200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>186700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>109600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>91600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>151500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>155100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>76200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>221100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>21400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>122300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>58300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>81000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>218500</v>
+      </c>
+      <c r="E35" s="3">
         <v>125100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>211900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>189600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>146100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>74200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>72400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-104000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>116000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>46700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>34100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>138500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>45900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>54000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>109000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>98000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>259800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>445300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>302300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>233600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>280300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>182300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>170700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>63200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>224000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>187200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>186700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>109600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>91600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>151500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>155100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>76200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>221100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>21400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>122300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>58300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>81000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,175 +4305,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2624800</v>
+      </c>
+      <c r="E41" s="3">
         <v>2436200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1387300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2911500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2031200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2045100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1718100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2953400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2048600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1506400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3605300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1579100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2245900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1983400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1224000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2361000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1745000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1704000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1228000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1954000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2222700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2026000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1275500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1512400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1523300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1050000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1486000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1711000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1412000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1337100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1467100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2205300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1226500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1176600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1387200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1141900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1166800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1047500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1006100</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1443300</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>103300</v>
+      </c>
+      <c r="E42" s="3">
         <v>81900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>78500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>80000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>82700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>62800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>85400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>55400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>56400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>77100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>55800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>55300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>55900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>53500</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4463,53 +4553,56 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1635500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1645400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1483700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1638000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1414000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1248300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1126100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1429300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1192400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1268200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1221600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1077600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1106900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>980300</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4585,8 +4678,11 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4629,8 +4725,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,8 +4803,11 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4751,8 +4850,8 @@
       <c r="P45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -4829,53 +4928,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4363600</v>
+      </c>
+      <c r="E46" s="3">
         <v>4163500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2949500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4629500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3527900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3356200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2929600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4438100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3297400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2851700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4882700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2712000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3408700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3017200</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4951,374 +5053,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>10468200</v>
+      </c>
+      <c r="E47" s="3">
         <v>9679600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9145500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8826400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8625500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8017200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7864800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7641800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7696100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7697500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7786100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7837100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8224800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8307600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>9799000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>10234000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>10657000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>11249000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>11613000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>11450200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>9954100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>9253100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>8349200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7823500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>7593200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>7445500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>7212300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>7277700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>7200600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>6991800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>6638500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>6637000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>6196700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>5893500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>5728100</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>5743600</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>5789900</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>5493600</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>5508500</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>5489500</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>857800</v>
+      </c>
+      <c r="E48" s="3">
         <v>866900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>891900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>902300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>924100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>951000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>966000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1013100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>996900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>984000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>982100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>967900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>943600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>907000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>885000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>851000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>824000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>766000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>755000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>716200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>705300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>700400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>715000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>714800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>741000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>783900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>738200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>740300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>756400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>767600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>457800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>457500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>446300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>435900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>439600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>438100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>433000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>429000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>434100</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>430600</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2593900</v>
+      </c>
+      <c r="E49" s="3">
         <v>2600300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2606000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2609200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2612200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2609600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2603400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2613800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2609600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2611100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2613700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2610300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2620700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2634200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1992000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2016000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2023000</v>
-      </c>
-      <c r="T49" s="3">
-        <v>1806000</v>
       </c>
       <c r="U49" s="3">
         <v>1806000</v>
       </c>
       <c r="V49" s="3">
+        <v>1806000</v>
+      </c>
+      <c r="W49" s="3">
         <v>1604900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1556000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1558200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1573100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1552000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1591900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1565500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1242700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1242600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1246700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1247800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1253500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1256700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1271200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1229400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1212900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1220600</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1109800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1095800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1096300</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>1066200</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,55 +5678,58 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>648100</v>
+      </c>
+      <c r="E52" s="3">
         <v>616900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>590800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>598800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>540400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>519600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>466600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>809500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>507200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>503400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>465700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>495800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>478600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>463000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>54000</v>
-      </c>
-      <c r="R52" s="3">
-        <v>14000</v>
       </c>
       <c r="S52" s="3">
         <v>14000</v>
@@ -5621,7 +5741,7 @@
         <v>14000</v>
       </c>
       <c r="V52" s="3">
-        <v>14500</v>
+        <v>14000</v>
       </c>
       <c r="W52" s="3">
         <v>14500</v>
@@ -5633,10 +5753,10 @@
         <v>14500</v>
       </c>
       <c r="Z52" s="3">
+        <v>14500</v>
+      </c>
+      <c r="AA52" s="3">
         <v>216600</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>18300</v>
       </c>
       <c r="AB52" s="3">
         <v>18300</v>
@@ -5645,7 +5765,7 @@
         <v>18300</v>
       </c>
       <c r="AD52" s="3">
-        <v>16600</v>
+        <v>18300</v>
       </c>
       <c r="AE52" s="3">
         <v>16600</v>
@@ -5657,7 +5777,7 @@
         <v>16600</v>
       </c>
       <c r="AH52" s="3">
-        <v>22800</v>
+        <v>16600</v>
       </c>
       <c r="AI52" s="3">
         <v>22800</v>
@@ -5669,7 +5789,7 @@
         <v>22800</v>
       </c>
       <c r="AL52" s="3">
-        <v>20000</v>
+        <v>22800</v>
       </c>
       <c r="AM52" s="3">
         <v>20000</v>
@@ -5681,10 +5801,13 @@
         <v>20000</v>
       </c>
       <c r="AP52" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AQ52" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>18941000</v>
+      </c>
+      <c r="E54" s="3">
         <v>17936600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16228800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17610000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16273900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15497400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14908600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16566400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15157300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14697800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16802800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14677600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15730900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15383500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14955000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16486000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16262000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16527000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>16451000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16686100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>15426900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>14431900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>12796000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>12638800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12288000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11675500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>11519200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11804100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>11443200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>11160300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>10630600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>11380100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>9959400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>9546800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>9573200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>9347000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>9314300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>8874400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>8831800</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>9246500</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,175 +6145,179 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2053700</v>
+      </c>
+      <c r="E57" s="3">
         <v>1958900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1217300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2126100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2072900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1911000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1260100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2127200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2159200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2006600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1345700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2110400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2111900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2035000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>915000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1115000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1015000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1051000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1262000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1252000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1070800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1113400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>979700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>830100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>781500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>664000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>820400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>812500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>709300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>631500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>778700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>826700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>770700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>709600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>793200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>741600</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>697000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>675800</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>794000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>813900</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1036500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1078600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>984400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1078400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>883800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>735800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>643800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>878200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>641500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>688800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>553300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>530400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>585700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>502900</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6259,175 +6393,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7933300</v>
+      </c>
+      <c r="E59" s="3">
         <v>7123000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5528300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6952600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>6055000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5698500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5248400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6086900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5633200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5318500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7484300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5621300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6377900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6204700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7124000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>8324000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7723000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7346000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6651000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>7043200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6920600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>6154000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4804500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4918800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4925200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4850100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4748700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5305000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5265900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>5344000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4837900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>5581000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4326100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4187700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4104100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>4079900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>4208900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>3926300</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>3815700</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>4302200</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11023500</v>
+      </c>
+      <c r="E60" s="3">
         <v>10160500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8492100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10157100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9011700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8345300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7855600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9092300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8433900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8013900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10039100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8262100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>9075500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8742600</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6503,130 +6643,136 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1752700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1751900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1685700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1766900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1769500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1775900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1776500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2089900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1636700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1631400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1640500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1647000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1656500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1659100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2012000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1988000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2075000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2205000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2186000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2242500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1619200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1655000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1526900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1538300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1489200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1288800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1006600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>961800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>919700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>858600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>808300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>821800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>832600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>731500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>732800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>734100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>734500</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>735500</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>736700</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>737900</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6669,23 +6815,23 @@
       <c r="P62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R62" s="3">
         <v>19000</v>
-      </c>
-      <c r="R62" s="3">
-        <v>314000</v>
       </c>
       <c r="S62" s="3">
         <v>314000</v>
       </c>
       <c r="T62" s="3">
-        <v>345000</v>
+        <v>314000</v>
       </c>
       <c r="U62" s="3">
         <v>345000</v>
       </c>
       <c r="V62" s="3">
-        <v>291200</v>
+        <v>345000</v>
       </c>
       <c r="W62" s="3">
         <v>291200</v>
@@ -6697,10 +6843,10 @@
         <v>291200</v>
       </c>
       <c r="Z62" s="3">
+        <v>291200</v>
+      </c>
+      <c r="AA62" s="3">
         <v>414400</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>266100</v>
       </c>
       <c r="AB62" s="3">
         <v>266100</v>
@@ -6709,7 +6855,7 @@
         <v>266100</v>
       </c>
       <c r="AD62" s="3">
-        <v>217100</v>
+        <v>266100</v>
       </c>
       <c r="AE62" s="3">
         <v>217100</v>
@@ -6721,7 +6867,7 @@
         <v>217100</v>
       </c>
       <c r="AH62" s="3">
-        <v>219300</v>
+        <v>217100</v>
       </c>
       <c r="AI62" s="3">
         <v>219300</v>
@@ -6733,7 +6879,7 @@
         <v>219300</v>
       </c>
       <c r="AL62" s="3">
-        <v>242200</v>
+        <v>219300</v>
       </c>
       <c r="AM62" s="3">
         <v>242200</v>
@@ -6745,10 +6891,13 @@
         <v>242200</v>
       </c>
       <c r="AP62" s="3">
+        <v>242200</v>
+      </c>
+      <c r="AQ62" s="3">
         <v>133100</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13297200</v>
+      </c>
+      <c r="E66" s="3">
         <v>12424400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10704500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>12284800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11124600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10456500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9981600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11455800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10324700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9891900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11940000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10135600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10944000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10604600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10290000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11978000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11346000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11164000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10684000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11088900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10163100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9476600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7886000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7915000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7722600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7316100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>7098700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7562000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>7358300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>7282200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6888800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>7705900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6389900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6076300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6093300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>6053200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>6120900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>5802000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>5823600</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>6224200</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4240800</v>
+      </c>
+      <c r="E72" s="3">
         <v>4079500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4011800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3857100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3724500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3634800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3617300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3601400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3761900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3701600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3710600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3739000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3796200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3712300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3721000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3722000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3775000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3721000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3680000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3476900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3088600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2837200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2655500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2426900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2294600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2173700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>2161000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1985100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1845900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1707100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1644200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1600300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1496600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1384700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1311100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1129000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1150600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1066700</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1046800</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>1012500</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5620800</v>
+      </c>
+      <c r="E76" s="3">
         <v>5489600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5499500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5301100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5126200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5019300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4908500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5092200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4813600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4787100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4848100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4527200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4772400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4756500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4665000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4508000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4916000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5363000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5767000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5597100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5263700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4955300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4910000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4723800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4565400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4359300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4420500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4242100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4084900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3878000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3741900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3674200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3569500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3470500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3480000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3293900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3193400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3072500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>3008200</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>3022300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>218500</v>
+      </c>
+      <c r="E81" s="3">
         <v>125100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>211900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>189600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>146100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>74200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>72400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-104000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>116000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>46700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>34100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>138500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>45900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>54000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>109000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>98000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>259800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>445300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>302300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>233600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>280300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>182300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>170700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>63200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>224000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>187200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>186700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>109600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>91600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>151500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>155100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>76200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>221100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>21400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>122300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>58300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>81000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E83" s="3">
         <v>42900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>41800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>42500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>40900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>37800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>37100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>34400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>33500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>32000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>30800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>29700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>27700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>26100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>43000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>41000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>42000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>41000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>39500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>39200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>40900</v>
-      </c>
-      <c r="X83" s="3">
-        <v>38300</v>
       </c>
       <c r="Y83" s="3">
         <v>38300</v>
       </c>
       <c r="Z83" s="3">
+        <v>38300</v>
+      </c>
+      <c r="AA83" s="3">
         <v>38200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>41000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>31400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>31500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>31700</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>32900</v>
       </c>
       <c r="AF83" s="3">
         <v>32900</v>
       </c>
       <c r="AG83" s="3">
+        <v>32900</v>
+      </c>
+      <c r="AH83" s="3">
         <v>33400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>31700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>31100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>29700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>31800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>36000</v>
-      </c>
-      <c r="AM83" s="3">
-        <v>30100</v>
       </c>
       <c r="AN83" s="3">
         <v>30100</v>
       </c>
       <c r="AO83" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AP83" s="3">
         <v>28100</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>356600</v>
+      </c>
+      <c r="E89" s="3">
         <v>5600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>369300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>272500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>361800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-52800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>324600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>236900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>266700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>69300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-41700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>219300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>269000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-92300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>247000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>304000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>189000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>40000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>344000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>399000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>253100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>223900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>425200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>291500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>343800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>24200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>301400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>310600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>266600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>34500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>308300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>230800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>210900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>43200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>176600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>220900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>228500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>6100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>237200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>105800</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-39200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-38300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-44800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-49400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-52400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-41700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-58400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-51500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-56700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-51700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-58100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-65800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-76400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-63100</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-71000</v>
       </c>
       <c r="R91" s="3">
         <v>-71000</v>
       </c>
       <c r="S91" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="T91" s="3">
         <v>-75000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-43000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-49900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-43500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-39000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-28600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-22500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-33600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-28800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-29200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-28800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-24200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-26600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-27400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-30900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-31600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-33400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-22300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-31100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-33500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-39700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-29900</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-28500</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-42800</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-845100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-815700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-144500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-353700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-723200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-234500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-33100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-295000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>100800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-231400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>414700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-61100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-181000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>426900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-140000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-62000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-86000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-107000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-565000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1296100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-752600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-779300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-319500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-390100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-12700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-692800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-27200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-57700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-76700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-290600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-205900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-446800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-279300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-288700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>5000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-76400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-292000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-23700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-194200</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-145100</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,130 +10455,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E96" s="3">
         <v>56200</v>
-      </c>
-      <c r="E96" s="3">
-        <v>56000</v>
       </c>
       <c r="F96" s="3">
         <v>56000</v>
       </c>
       <c r="G96" s="3">
+        <v>56000</v>
+      </c>
+      <c r="H96" s="3">
         <v>55300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>55700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>55500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>55600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>54700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>54900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>54500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>54700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>53600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>53800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-53000</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-54000</v>
       </c>
       <c r="S96" s="3">
         <v>-54000</v>
       </c>
       <c r="T96" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-56000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-55900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-56000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-50100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-51000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-50900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-49100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-49000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-49700</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-47200</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-47100</v>
       </c>
       <c r="AE96" s="3">
         <v>-47100</v>
       </c>
       <c r="AF96" s="3">
+        <v>-47100</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-47000</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-46900</v>
       </c>
       <c r="AH96" s="3">
         <v>-46900</v>
       </c>
       <c r="AI96" s="3">
+        <v>-46900</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-42400</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-42300</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-42100</v>
       </c>
       <c r="AL96" s="3">
         <v>-42100</v>
       </c>
       <c r="AM96" s="3">
+        <v>-42100</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-37600</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-37500</v>
-      </c>
-      <c r="AO96" s="3">
-        <v>-37300</v>
       </c>
       <c r="AP96" s="3">
         <v>-37300</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-37300</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>677800</v>
+      </c>
+      <c r="E100" s="3">
         <v>1862700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1751500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>964900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>335500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>612300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1509200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>957000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>175000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1932200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1648000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-820000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>171400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>423700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1250000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>385000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-54000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>543000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-507400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>634100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>694200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1305100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-351800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>83300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>137800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>244600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-503200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>49600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-115400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>124000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-836700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1197000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>120500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>33900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>63100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-172600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>179800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>57700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-475400</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>241200</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E101" s="3">
         <v>2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-17600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>5200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>6200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-10600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-8600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>6000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-11000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-8000</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>2800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-5600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>9200</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>4400</v>
       </c>
       <c r="AA101" s="3">
         <v>4400</v>
       </c>
       <c r="AB101" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-11900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>4000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>2000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-3900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>3300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>3000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>1300</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-4800</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>188600</v>
+      </c>
+      <c r="E102" s="3">
         <v>1048900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1524200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>880300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-13900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>327000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1235300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>904800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>542200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2098900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2026200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-666800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>262500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>759900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1137000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>616000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>41000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>476000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-725500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-268700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>196700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>750600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-236900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>473400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-436000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-225000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>299000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>74900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-130100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-738200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>978800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>49900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-210600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>245300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-24800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>119300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>41300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-437200</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>201500</v>
       </c>
     </row>
